--- a/회원사_관리.xlsx
+++ b/회원사_관리.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52948055-9B55-49C1-8121-271BF8D2A1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="32385" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="회원사" state="visible" r:id="rId4"/>
+    <sheet name="회원사" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
   <si>
     <t>▶ 회원사 정보를 입력한 뒤 저장하고, 터미널에서  npm run import:partners  실행 → 사이트에 반영됩니다. (열 제목은 바꾸지 마세요)</t>
   </si>
@@ -37,36 +41,15 @@
     <t>홈페이지</t>
   </si>
   <si>
-    <t>대경IT 본부</t>
-  </si>
-  <si>
-    <t>IT 인프라 · NAS · 네트워크</t>
-  </si>
-  <si>
     <t>대구</t>
   </si>
   <si>
-    <t>대구광역시 중구 동성로2가</t>
-  </si>
-  <si>
     <t>대표자명</t>
   </si>
   <si>
     <t>053-000-0000</t>
   </si>
   <si>
-    <t>https://hanbyeolsystem.github.io/dk-it/</t>
-  </si>
-  <si>
-    <t>(주)○○시스템</t>
-  </si>
-  <si>
-    <t>서버 · 보안 솔루션</t>
-  </si>
-  <si>
-    <t>대구광역시 수성구 달구벌대로</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -161,28 +144,106 @@
   </si>
   <si>
     <t>경상북도 칠곡군 왜관읍 중앙로</t>
+  </si>
+  <si>
+    <t>한별시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터.프린터.나스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 달서구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구광역시 달서구 문화회관11안길 22-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김상환</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-588-7119</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://한별시스템.kr</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>디직스코리아</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 문경</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">컴퓨터미및주변기기 복합기 CCTV 키드체크기,POS,키오스크 사무기기렌탈 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 문경시 신흥로130 상가1층 디직스코리아</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤일한</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>054-555-4949</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/1886346752?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606271548%26locale%3Dko%26svcName%3Dmap_pcv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFDD5A12"/>
-      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -216,20 +277,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -565,9 +629,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -578,275 +642,280 @@
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C11" t="s">
         <v>37</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D11" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B12" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C12" t="s">
         <v>41</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D12" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{D578B476-1692-4255-A081-4A0A6E7F0472}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{A8BF0B46-5BF1-4D63-98BC-13956F60B3BC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId3"/>
 </worksheet>
 </file>
--- a/회원사_관리.xlsx
+++ b/회원사_관리.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52948055-9B55-49C1-8121-271BF8D2A1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47583FBC-7942-44A8-BA7D-671E2A812002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32385" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,190 +15,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+  <si>
+    <t>업체명 (필수)</t>
+  </si>
+  <si>
+    <t>전문분야</t>
+  </si>
+  <si>
+    <t>지역</t>
+  </si>
+  <si>
+    <t>주소 (지도표시·필수)</t>
+  </si>
+  <si>
+    <t>대표자</t>
+  </si>
+  <si>
+    <t>대표전화</t>
+  </si>
+  <si>
+    <t>홈페이지</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>한별시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 달서구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구광역시 달서구 문화회관11안길 22-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김상환</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-588-7119</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://한별시스템.kr</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>디직스코리아</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 문경</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 문경시 신흥로130 상가1층 디직스코리아</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤일한</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>054-555-4949</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/1886346752?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606271548%26locale%3Dko%26svcName%3Dmap_pcv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이스시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-857-9595</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경산 하양</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 경산시 하양읍 금송로 17</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>황동훈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/15199737?placePath=%2Fhome%3Fentry%3Dplt%26from%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606281738%26locale%3Dko%26svcName%3Dmap_pcv5&amp;searchType=place&amp;lng=128.8175301&amp;lat=35.9147786&amp;c=15.00,0,0,0,dh</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
   <si>
     <t>▶ 회원사 정보를 입력한 뒤 저장하고, 터미널에서  npm run import:partners  실행 → 사이트에 반영됩니다. (열 제목은 바꾸지 마세요)</t>
-  </si>
-  <si>
-    <t>업체명 (필수)</t>
-  </si>
-  <si>
-    <t>전문분야</t>
-  </si>
-  <si>
-    <t>지역</t>
-  </si>
-  <si>
-    <t>주소 (지도표시·필수)</t>
-  </si>
-  <si>
-    <t>대표자</t>
-  </si>
-  <si>
-    <t>대표전화</t>
-  </si>
-  <si>
-    <t>홈페이지</t>
-  </si>
-  <si>
-    <t>대구</t>
-  </si>
-  <si>
-    <t>대표자명</t>
-  </si>
-  <si>
-    <t>053-000-0000</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>(주)○○네트웍스</t>
-  </si>
-  <si>
-    <t>네트워크 · 통신 구축</t>
-  </si>
-  <si>
-    <t>대구광역시 달서구 성서공단로</t>
-  </si>
-  <si>
-    <t>○○정보통신</t>
-  </si>
-  <si>
-    <t>CCTV · 출입통제</t>
-  </si>
-  <si>
-    <t>경북 구미</t>
-  </si>
-  <si>
-    <t>경상북도 구미시 송정대로</t>
-  </si>
-  <si>
-    <t>054-000-0000</t>
-  </si>
-  <si>
-    <t>(주)○○테크</t>
-  </si>
-  <si>
-    <t>사무기기 · 복합기 임대</t>
-  </si>
-  <si>
-    <t>경북 포항</t>
-  </si>
-  <si>
-    <t>경상북도 포항시 북구 중앙로</t>
-  </si>
-  <si>
-    <t>○○솔루션</t>
-  </si>
-  <si>
-    <t>데이터 백업 · 복구</t>
-  </si>
-  <si>
-    <t>경북 경산</t>
-  </si>
-  <si>
-    <t>경상북도 경산시 경안로</t>
-  </si>
-  <si>
-    <t>(주)○○ICT</t>
-  </si>
-  <si>
-    <t>클라우드 · 가상화</t>
-  </si>
-  <si>
-    <t>대구광역시 북구 칠성로</t>
-  </si>
-  <si>
-    <t>○○컴퓨터</t>
-  </si>
-  <si>
-    <t>PC · 노트북 유지보수</t>
-  </si>
-  <si>
-    <t>경북 안동</t>
-  </si>
-  <si>
-    <t>경상북도 안동시 경동로</t>
-  </si>
-  <si>
-    <t>(주)○○전산</t>
-  </si>
-  <si>
-    <t>ERP · 그룹웨어</t>
-  </si>
-  <si>
-    <t>경북 경주</t>
-  </si>
-  <si>
-    <t>경상북도 경주시 원화로</t>
-  </si>
-  <si>
-    <t>○○시스템즈</t>
-  </si>
-  <si>
-    <t>산업용 네트워크</t>
-  </si>
-  <si>
-    <t>경북 칠곡</t>
-  </si>
-  <si>
-    <t>경상북도 칠곡군 왜관읍 중앙로</t>
-  </si>
-  <si>
-    <t>한별시스템</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>컴퓨터.프린터.나스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대구 달서구</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대구광역시 달서구 문화회관11안길 22-7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>김상환</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>053-588-7119</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://한별시스템.kr</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>디직스코리아</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>경북 문경</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">컴퓨터미및주변기기 복합기 CCTV 키드체크기,POS,키오스크 사무기기렌탈 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>경북 문경시 신흥로130 상가1층 디직스코리아</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>윤일한</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>054-555-4949</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://map.naver.com/p/entry/place/1886346752?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606271548%26locale%3Dko%26svcName%3Dmap_pcv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터, 사무기기, CCTV, 삼성/중소기업TV</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">컴퓨터 및 주변기기 복합기 CCTV 키드체크기,POS,키오스크 사무기기렌탈 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터, 프린터, 나스, 핸드프린터, 라벨프린터 판매 및 렌탈</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -286,10 +213,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -643,267 +570,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>49</v>
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>56</v>
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>19</v>
-      </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -914,8 +715,9 @@
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{D578B476-1692-4255-A081-4A0A6E7F0472}"/>
     <hyperlink ref="G4" r:id="rId2" xr:uid="{A8BF0B46-5BF1-4D63-98BC-13956F60B3BC}"/>
+    <hyperlink ref="G5" r:id="rId3" display="https://map.naver.com/p/entry/place/15199737?placePath=%2Fhome%3Fentry%3Dplt%26from%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606281738%26locale%3Dko%26svcName%3Dmap_pcv5&amp;searchType=place&amp;lng=128.8175301&amp;lat=35.9147786&amp;c=15.00,0,0,0,dh" xr:uid="{4ED81662-4740-49DE-B0E6-53D9CD31F2B4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId4"/>
 </worksheet>
 </file>
--- a/회원사_관리.xlsx
+++ b/회원사_관리.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47583FBC-7942-44A8-BA7D-671E2A812002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26F979E-CA1C-455C-A461-70FD01D93896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32385" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>업체명 (필수)</t>
   </si>
@@ -38,9 +38,6 @@
     <t>홈페이지</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>한별시스템</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -126,6 +123,215 @@
   </si>
   <si>
     <t>컴퓨터, 프린터, 나스, 핸드프린터, 라벨프린터 판매 및 렌탈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>위더스컴퓨터(월배이마트점)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-639-1579 / 010-7207-1579</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구시 달서구 조암남로135</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수민</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터, 프린터임대 ,
+사무기기렌탈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다원시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-742-3411</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 남구 대봉로30길37</t>
+  </si>
+  <si>
+    <t>컴퓨터및주변기기, 디지털복합기.CCTV.사무기기렌탈, 음향.빔프로젝트.LED전광판공사.렌탈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장순철</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 남구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>제이씨스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 경산시 원효로28길60-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경산</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터 주변기기 바코드장비 소모품 네트워크 기업장비유지보수</t>
+  </si>
+  <si>
+    <t>053-813-0431</t>
+  </si>
+  <si>
+    <t>박준영</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 북구 유통단지로25 4동 301호</t>
+  </si>
+  <si>
+    <t>070-7530-3348</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김세용</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>라인시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이타 복구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 북구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>베스트잉크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 달성군 화원읍 성천로108</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터  프린터 렌탈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-2431-5544</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>조재현</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유원비즈텍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 화원</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 성서공단</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구시 수성구 동대구로 55길 4-5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>영업 관리시스템 개발, 홈페이지 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://uonebiztec.com/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장승도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-767-2701</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>피씨플래너</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-604-5250</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구시 북구 유통단지로45 3증319호</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복사기 · 프린터 판매 및 렌탈, 컴퓨터 주변기기 및 유지보수, CAM/NC 프로그래밍 MCT(머시닝센터) 가공 지원 및 기술지원, 데이터 복구,네트워크 구축 및 유지보수, LAN(랜) 공사 및 통신</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 전자관</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김년오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴셋시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구시달서구용산큰못1길7 1층 위더스컴퓨터</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터수리. 조립. 판매. 중고부속 취급 업체유지보수.네트워크공사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 용산</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정홍욱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>053-554 4551 / 010-2914-8722</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/1539410457?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606290936%26locale%3Dko%26svcName%3Dmap_pcv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/search/%EC%9B%90%ED%9A%A8%EB%A1%9C28%EA%B8%B860-7/place/1239353629?c=15.00,0,0,0,dh&amp;isCorrectAnswer=true&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606290936%26locale%3Dko%26svcName%3Dmap_pcv5%26searchText%3D%EC%9B%90%ED%9A%A8%EB%A1%9C28%EA%B8%B860-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/1034783011?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606290938%26locale%3Dko%26svcName%3Dmap_pcv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/1829807055?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606290939%26locale%3Dko%26svcName%3Dmap_pcv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/1469733822?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606290939%26locale%3Dko%26svcName%3Dmap_pcv5</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -208,7 +414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -216,6 +422,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -557,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -565,13 +774,13 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="6" max="6" width="29.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -605,106 +814,246 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G7" t="s">
-        <v>7</v>
+    </row>
+    <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G8" t="s">
-        <v>7</v>
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G9" t="s">
-        <v>7</v>
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G10" t="s">
-        <v>7</v>
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G11" t="s">
-        <v>7</v>
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G12" t="s">
-        <v>7</v>
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -716,8 +1065,14 @@
     <hyperlink ref="G3" r:id="rId1" xr:uid="{D578B476-1692-4255-A081-4A0A6E7F0472}"/>
     <hyperlink ref="G4" r:id="rId2" xr:uid="{A8BF0B46-5BF1-4D63-98BC-13956F60B3BC}"/>
     <hyperlink ref="G5" r:id="rId3" display="https://map.naver.com/p/entry/place/15199737?placePath=%2Fhome%3Fentry%3Dplt%26from%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606281738%26locale%3Dko%26svcName%3Dmap_pcv5&amp;searchType=place&amp;lng=128.8175301&amp;lat=35.9147786&amp;c=15.00,0,0,0,dh" xr:uid="{4ED81662-4740-49DE-B0E6-53D9CD31F2B4}"/>
+    <hyperlink ref="G11" r:id="rId4" xr:uid="{D61AB269-3619-4426-9E10-46F62A4C9099}"/>
+    <hyperlink ref="G13" r:id="rId5" xr:uid="{A3DC533D-ABB6-4D15-A8C7-41B00A2BD79E}"/>
+    <hyperlink ref="G12" r:id="rId6" xr:uid="{61BB5B91-2AA2-4738-BD3B-9287EC426DC3}"/>
+    <hyperlink ref="G8" r:id="rId7" display="https://map.naver.com/p/search/%EC%9B%90%ED%9A%A8%EB%A1%9C28%EA%B8%B860-7/place/1239353629?c=15.00,0,0,0,dh&amp;isCorrectAnswer=true&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606290936%26locale%3Dko%26svcName%3Dmap_pcv5%26searchText%3D%EC%9B%90%ED%9A%A8%EB%A1%9C28%EA%B8%B860-7" xr:uid="{2FB3087C-4EB6-490E-B547-BBB24DF23DE5}"/>
+    <hyperlink ref="G7" r:id="rId8" xr:uid="{065F1D56-40E5-411F-84EE-8865CBB4C7FF}"/>
+    <hyperlink ref="G6" r:id="rId9" xr:uid="{2A13C005-CAB5-41F7-9AE2-328B953C0C0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId4"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId10"/>
 </worksheet>
 </file>
--- a/회원사_관리.xlsx
+++ b/회원사_관리.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26F979E-CA1C-455C-A461-70FD01D93896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EB856E-D67B-4E46-B510-18200CC8E9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32385" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>업체명 (필수)</t>
   </si>
@@ -39,10 +39,6 @@
   </si>
   <si>
     <t>한별시스템</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대구 달서구</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -332,6 +328,14 @@
   </si>
   <si>
     <t>https://map.naver.com/p/entry/place/1469733822?c=15.00,0,0,0,dh&amp;placePath=%2Fhome%3Ffrom%3Dmap%26fromPanelNum%3D1%26additionalHeight%3D76%26timestamp%3D202606290939%26locale%3Dko%26svcName%3Dmap_pcv5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 수성구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구 월배</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -420,11 +424,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -779,15 +783,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -817,243 +821,246 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
       <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
         <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
         <v>52</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
         <v>54</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
         <v>65</v>
       </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
         <v>71</v>
       </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>74</v>
       </c>
-      <c r="D13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>75</v>
       </c>
-      <c r="F13" t="s">
-        <v>76</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
